--- a/storage/app/templates/documents/TEMPLAT_LS_DPUPR.xlsx
+++ b/storage/app/templates/documents/TEMPLAT_LS_DPUPR.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALFIAN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APPS\laragon\www\sipraja\storage\app\templates\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8461D77-E966-42BC-A2CD-21FB8D40DC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B67AD2-CEDD-47DD-83DF-10E29712ACE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
   <si>
     <t>Kode SKPD</t>
   </si>
@@ -242,6 +253,9 @@
   </si>
   <si>
     <t>198206042010012000</t>
+  </si>
+  <si>
+    <t>1 Januari 2025</t>
   </si>
 </sst>
 </file>
@@ -285,13 +299,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,13 +638,13 @@
     <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="148.85546875" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -639,10 +654,10 @@
     <col min="38" max="38" width="50" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="50" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12" style="5" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12" style="6" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="50" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="15.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="14" style="3" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -730,7 +745,7 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Z1" t="s">
@@ -748,7 +763,7 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
       <c r="AF1" t="s">
@@ -778,16 +793,16 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AP1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="6" t="s">
         <v>43</v>
       </c>
       <c r="AS1" s="2" t="s">
@@ -864,8 +879,8 @@
       <c r="W2" t="s">
         <v>63</v>
       </c>
-      <c r="Y2" s="5">
-        <v>45676</v>
+      <c r="Y2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="Z2" t="s">
         <v>64</v>
@@ -882,8 +897,8 @@
       <c r="AD2" t="s">
         <v>65</v>
       </c>
-      <c r="AE2" s="5">
-        <v>45707</v>
+      <c r="AE2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="AF2" t="s">
         <v>66</v>
@@ -912,17 +927,17 @@
       <c r="AN2" t="s">
         <v>71</v>
       </c>
-      <c r="AO2" s="5">
-        <v>45707</v>
+      <c r="AO2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="AP2" t="s">
         <v>72</v>
       </c>
-      <c r="AQ2" s="5">
-        <v>45708</v>
-      </c>
-      <c r="AR2" s="5">
-        <v>45708</v>
+      <c r="AQ2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="AS2" s="3">
         <v>641916000</v>
